--- a/labeled/Add_Eating/July/multi_seed_results/seed_ranking_summary.xlsx
+++ b/labeled/Add_Eating/July/multi_seed_results/seed_ranking_summary.xlsx
@@ -470,16 +470,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.9576502654770533</v>
+        <v>0.9080563536941184</v>
       </c>
       <c r="D2" t="n">
-        <v>5.022766477179032</v>
+        <v>7.289693369896095</v>
       </c>
       <c r="E2" t="n">
-        <v>68.41844823239339</v>
+        <v>232.4483695049146</v>
       </c>
       <c r="F2" t="n">
-        <v>145</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>101</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.9525961026646873</v>
+        <v>0.8126825356965968</v>
       </c>
       <c r="D3" t="n">
-        <v>5.659494703893949</v>
+        <v>7.276234960914843</v>
       </c>
       <c r="E3" t="n">
-        <v>53.53107835352403</v>
+        <v>149.4904956901219</v>
       </c>
       <c r="F3" t="n">
-        <v>145</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>123</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.9522639418500861</v>
+        <v>0.7890843228750608</v>
       </c>
       <c r="D4" t="n">
-        <v>5.419684971705257</v>
+        <v>8.415175910915435</v>
       </c>
       <c r="E4" t="n">
-        <v>53.36137810795763</v>
+        <v>62.30463562544139</v>
       </c>
       <c r="F4" t="n">
-        <v>145</v>
+        <v>93</v>
       </c>
     </row>
     <row r="5">
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>505</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.9479125924700312</v>
+        <v>0.7524206856742748</v>
       </c>
       <c r="D5" t="n">
-        <v>5.70453803734484</v>
+        <v>7.791193565373569</v>
       </c>
       <c r="E5" t="n">
-        <v>60.21710508049315</v>
+        <v>314.0543439515895</v>
       </c>
       <c r="F5" t="n">
-        <v>145</v>
+        <v>93</v>
       </c>
     </row>
     <row r="6">
@@ -554,20 +554,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>505</t>
+          <t>789</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.92523229038287</v>
+        <v>0.7376040068720785</v>
       </c>
       <c r="D6" t="n">
-        <v>6.65389157567495</v>
+        <v>8.361956697179181</v>
       </c>
       <c r="E6" t="n">
-        <v>94.92898731550629</v>
+        <v>61.09256958163822</v>
       </c>
       <c r="F6" t="n">
-        <v>145</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7">
@@ -580,16 +580,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.9191541738913238</v>
+        <v>0.7146018935067739</v>
       </c>
       <c r="D7" t="n">
-        <v>6.984537691503951</v>
+        <v>10.57996334414185</v>
       </c>
       <c r="E7" t="n">
-        <v>53.3954905505979</v>
+        <v>321.9391372563247</v>
       </c>
       <c r="F7" t="n">
-        <v>145</v>
+        <v>93</v>
       </c>
     </row>
     <row r="8">
@@ -598,20 +598,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>789</t>
+          <t>202</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.906771376010725</v>
+        <v>0.6687022265345008</v>
       </c>
       <c r="D8" t="n">
-        <v>7.423160711783551</v>
+        <v>11.06777555946434</v>
       </c>
       <c r="E8" t="n">
-        <v>59.15432322166529</v>
+        <v>151.6923117452558</v>
       </c>
       <c r="F8" t="n">
-        <v>145</v>
+        <v>93</v>
       </c>
     </row>
     <row r="9">
@@ -620,20 +620,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>42</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.9066396705293298</v>
+        <v>0.6538397940683407</v>
       </c>
       <c r="D9" t="n">
-        <v>7.269864998147138</v>
+        <v>10.23594565323895</v>
       </c>
       <c r="E9" t="n">
-        <v>43.094918069282</v>
+        <v>100.1020580007257</v>
       </c>
       <c r="F9" t="n">
-        <v>145</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10">
@@ -646,16 +646,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.9049498309174918</v>
+        <v>0.5379631865588981</v>
       </c>
       <c r="D10" t="n">
-        <v>8.457675796609642</v>
+        <v>15.73195409179443</v>
       </c>
       <c r="E10" t="n">
-        <v>68.00521788267534</v>
+        <v>124.9829120065634</v>
       </c>
       <c r="F10" t="n">
-        <v>145</v>
+        <v>93</v>
       </c>
     </row>
     <row r="11">
@@ -664,20 +664,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>303</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.8980578387715901</v>
+        <v>0.4768519768008288</v>
       </c>
       <c r="D11" t="n">
-        <v>7.63844356318076</v>
+        <v>10.82464434183965</v>
       </c>
       <c r="E11" t="n">
-        <v>47.30894640782788</v>
+        <v>87.53803368860591</v>
       </c>
       <c r="F11" t="n">
-        <v>145</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
